--- a/Archaeos Measurements.xlsx
+++ b/Archaeos Measurements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paoloattanasio/Documents/GitHub/Archaeos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandtgibson/Documents/GitHub/Archaeos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67B174A-4873-F444-B2A1-B5C8C7E58386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16CB92D-EDAC-EF46-B60E-807E420C8649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="500" windowWidth="53560" windowHeight="32880" xr2:uid="{583A5FEB-AE4E-B242-A25F-127587735FEC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20760" xr2:uid="{583A5FEB-AE4E-B242-A25F-127587735FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="181">
   <si>
     <t>P48483</t>
   </si>
@@ -727,6 +727,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -737,9 +740,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1075,7 +1075,7 @@
     <col min="17" max="19" width="14.5" style="2" customWidth="1"/>
     <col min="20" max="20" width="10.83203125" style="2"/>
     <col min="21" max="21" width="29.33203125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="11.1640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="47.5" style="2" customWidth="1"/>
     <col min="23" max="23" width="67.33203125" style="2" customWidth="1"/>
     <col min="24" max="24" width="13.83203125" style="2" customWidth="1"/>
     <col min="25" max="16384" width="10.83203125" style="2"/>
@@ -1145,7 +1145,7 @@
       <c r="U1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="V1" s="7" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1215,7 +1215,10 @@
       <c r="T2" s="10">
         <v>33378.150999999998</v>
       </c>
-      <c r="W2" s="16" t="s">
+      <c r="V2" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>179</v>
       </c>
     </row>
@@ -1285,7 +1288,10 @@
       <c r="T3" s="10">
         <v>33378.150999999998</v>
       </c>
-      <c r="W3" s="16"/>
+      <c r="V3" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W3" s="17"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -1353,7 +1359,10 @@
       <c r="T4" s="10">
         <v>33378.150999999998</v>
       </c>
-      <c r="W4" s="16"/>
+      <c r="V4" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W4" s="17"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -1421,7 +1430,10 @@
       <c r="T5" s="10">
         <v>33378.150999999998</v>
       </c>
-      <c r="W5" s="17" t="s">
+      <c r="V5" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W5" s="18" t="s">
         <v>167</v>
       </c>
     </row>
@@ -1477,7 +1489,10 @@
       <c r="T6" s="10">
         <v>33378.150999999998</v>
       </c>
-      <c r="W6" s="17"/>
+      <c r="V6" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W6" s="18"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -1545,7 +1560,10 @@
       <c r="T7" s="12">
         <v>8760</v>
       </c>
-      <c r="W7" s="17"/>
+      <c r="V7" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W7" s="18"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
@@ -1613,7 +1631,10 @@
       <c r="T8" s="12">
         <v>8760</v>
       </c>
-      <c r="W8" s="18" t="s">
+      <c r="V8" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W8" s="19" t="s">
         <v>168</v>
       </c>
     </row>
@@ -1683,7 +1704,10 @@
       <c r="T9" s="12">
         <v>8760</v>
       </c>
-      <c r="W9" s="18"/>
+      <c r="V9" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W9" s="19"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
@@ -1751,7 +1775,10 @@
       <c r="T10" s="12">
         <v>8760</v>
       </c>
-      <c r="W10" s="18"/>
+      <c r="V10" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W10" s="19"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -1819,7 +1846,10 @@
       <c r="T11" s="12">
         <v>8760</v>
       </c>
-      <c r="W11" s="19" t="s">
+      <c r="V11" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W11" s="20" t="s">
         <v>169</v>
       </c>
     </row>
@@ -1870,7 +1900,10 @@
       <c r="T12" s="12">
         <v>8760</v>
       </c>
-      <c r="W12" s="19"/>
+      <c r="V12" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="W12" s="20"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -1938,7 +1971,7 @@
       <c r="T13" s="5">
         <v>21140</v>
       </c>
-      <c r="W13" s="19"/>
+      <c r="W13" s="20"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -2216,7 +2249,7 @@
       <c r="T17" s="6">
         <v>50000</v>
       </c>
-      <c r="W17" s="20" t="s">
+      <c r="W17" s="16" t="s">
         <v>180</v>
       </c>
     </row>
